--- a/data/trans_orig/P19C10_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P19C10_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por dolor de mandíbula / solo 2023 en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue por dolor de mandíbula / solo 2023 en 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5064</t>
+          <t>5087</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13736</t>
+          <t>13865</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5167</t>
+          <t>5397</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14139</t>
+          <t>14324</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>483008</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>484441</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>707880</t>
+          <t>707751</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>716552</t>
+          <t>716529</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1191918</t>
+          <t>1191733</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1200890</t>
+          <t>1200660</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t>3308</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16454</t>
+          <t>16774</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2554</t>
+          <t>2570</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12240</t>
+          <t>12259</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7551</t>
+          <t>7567</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23971</t>
+          <t>24454</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2214083</t>
+          <t>2213763</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2227396</t>
+          <t>2227229</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2185666</t>
+          <t>2185647</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2195352</t>
+          <t>2195336</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4404471</t>
+          <t>4403988</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4420891</t>
+          <t>4420875</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10626</t>
+          <t>11305</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11065</t>
+          <t>10834</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3379</t>
+          <t>3335</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14858</t>
+          <t>14976</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>620690</t>
+          <t>620011</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>640546</t>
+          <t>640777</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>649729</t>
+          <t>649539</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1268069</t>
+          <t>1267951</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1279548</t>
+          <t>1279592</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>4726</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19329</t>
+          <t>19141</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13042</t>
+          <t>13155</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29245</t>
+          <t>28363</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20443</t>
+          <t>21643</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42137</t>
+          <t>43409</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3326964</t>
+          <t>3327152</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3342130</t>
+          <t>3341567</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3541888</t>
+          <t>3542770</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3558091</t>
+          <t>3557978</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1937,17 +1937,17 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6887287</t>
+          <t>6887288</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6875289</t>
+          <t>6874018</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6896983</t>
+          <t>6895784</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>6917426</t>
+          <t>6917427</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6917426</t>
+          <t>6917427</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6917426</t>
+          <t>6917427</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">

--- a/data/trans_orig/P19C10_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P19C10_2023-Estudios-trans_orig.xlsx
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8902</t>
+          <t>10489</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5087</t>
+          <t>6318</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13865</t>
+          <t>16725</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>8902</t>
+          <t>10489</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5397</t>
+          <t>6251</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14324</t>
+          <t>17052</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>484441</t>
+          <t>537279</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>712714</t>
+          <t>774103</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>707751</t>
+          <t>767867</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>716529</t>
+          <t>778274</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1197155</t>
+          <t>1311382</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1191733</t>
+          <t>1304819</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1200660</t>
+          <t>1315620</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>484441</t>
+          <t>537279</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>484441</t>
+          <t>537279</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>484441</t>
+          <t>537279</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>721616</t>
+          <t>784592</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>721616</t>
+          <t>784592</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>721616</t>
+          <t>784592</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1206057</t>
+          <t>1321871</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1206057</t>
+          <t>1321871</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1206057</t>
+          <t>1321871</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>8413</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3308</t>
+          <t>3511</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16774</t>
+          <t>16945</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5854</t>
+          <t>6920</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2570</t>
+          <t>3404</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12259</t>
+          <t>13768</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>14011</t>
+          <t>15333</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7567</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24454</t>
+          <t>26036</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2222380</t>
+          <t>2138065</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2213763</t>
+          <t>2129533</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2227229</t>
+          <t>2142967</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2192052</t>
+          <t>2103672</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2185647</t>
+          <t>2096824</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2195336</t>
+          <t>2107188</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4414431</t>
+          <t>4241737</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4403988</t>
+          <t>4231034</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4420875</t>
+          <t>4248070</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2230537</t>
+          <t>2146478</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2230537</t>
+          <t>2146478</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2230537</t>
+          <t>2146478</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2197906</t>
+          <t>2110592</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2197906</t>
+          <t>2110592</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2197906</t>
+          <t>2110592</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4428442</t>
+          <t>4257070</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4428442</t>
+          <t>4257070</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4428442</t>
+          <t>4257070</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>2342</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11305</t>
+          <t>10567</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5106</t>
+          <t>5576</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2072</t>
+          <t>2522</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10834</t>
+          <t>11821</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>7917</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3335</t>
+          <t>3908</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14976</t>
+          <t>16393</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -1524,27 +1524,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>629196</t>
+          <t>699499</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>620011</t>
+          <t>691274</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>631316</t>
+          <t>701841</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>646505</t>
+          <t>718837</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>640777</t>
+          <t>712592</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>649539</t>
+          <t>721891</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,17 +1594,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1275702</t>
+          <t>1418337</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1267951</t>
+          <t>1409861</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1279592</t>
+          <t>1422346</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>631316</t>
+          <t>701841</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>631316</t>
+          <t>701841</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>631316</t>
+          <t>701841</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>651611</t>
+          <t>724413</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>651611</t>
+          <t>724413</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>651611</t>
+          <t>724413</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1282927</t>
+          <t>1426254</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1282927</t>
+          <t>1426254</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1282927</t>
+          <t>1426254</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,27 +1754,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10277</t>
+          <t>10755</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4726</t>
+          <t>5174</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19141</t>
+          <t>19253</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19862</t>
+          <t>22984</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13155</t>
+          <t>15816</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28363</t>
+          <t>31750</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>30139</t>
+          <t>33739</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21643</t>
+          <t>23964</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43409</t>
+          <t>46275</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -1867,22 +1867,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3336016</t>
+          <t>3374843</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3327152</t>
+          <t>3366345</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3341567</t>
+          <t>3380424</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3551271</t>
+          <t>3596613</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3542770</t>
+          <t>3587847</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3557978</t>
+          <t>3603781</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6887288</t>
+          <t>6971456</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6874018</t>
+          <t>6958920</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6895784</t>
+          <t>6981231</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3346293</t>
+          <t>3385598</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3346293</t>
+          <t>3385598</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3346293</t>
+          <t>3385598</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3571133</t>
+          <t>3619597</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3571133</t>
+          <t>3619597</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3571133</t>
+          <t>3619597</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>6917427</t>
+          <t>7005195</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6917427</t>
+          <t>7005195</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6917427</t>
+          <t>7005195</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
